--- a/1_Admission_vital_signs.xlsx
+++ b/1_Admission_vital_signs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D4YKH4\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wrk\phd\HIS_Forms_for_Stroke_Care\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C83EED9-6308-4FF4-8705-234CB32ECB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14FF283D-6BE0-49BC-BC35-0534CE2D50F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="741" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="60">
   <si>
     <t>Block</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>Monitoring</t>
-  </si>
-  <si>
-    <t>Pulse</t>
   </si>
   <si>
     <t>Number field</t>
@@ -327,6 +324,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -340,9 +340,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -684,25 +681,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1"/>
@@ -714,22 +711,22 @@
       <c r="N1" s="2"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
@@ -740,20 +737,20 @@
       <c r="N2" s="2"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A3" s="8"/>
+      <c r="A3" s="9"/>
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="2"/>
@@ -764,20 +761,20 @@
       <c r="N3" s="2"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A4" s="9"/>
+      <c r="A4" s="10"/>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="2"/>
@@ -789,21 +786,21 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
@@ -814,22 +811,22 @@
       <c r="N5" s="2"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="C6" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="2"/>
@@ -840,20 +837,20 @@
       <c r="N6" s="2"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A7" s="8"/>
+      <c r="A7" s="9"/>
       <c r="B7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="2"/>
@@ -864,20 +861,20 @@
       <c r="N7" s="2"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A8" s="8"/>
+      <c r="A8" s="9"/>
       <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
@@ -888,20 +885,20 @@
       <c r="N8" s="2"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A9" s="9"/>
+      <c r="A9" s="10"/>
       <c r="B9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="2"/>
@@ -912,22 +909,22 @@
       <c r="N9" s="2"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="C10" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -938,18 +935,18 @@
       <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A11" s="9"/>
+      <c r="A11" s="10"/>
       <c r="B11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -960,17 +957,17 @@
       <c r="N11" s="2"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="D12" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -984,11 +981,11 @@
       <c r="N12" s="2"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A13" s="11"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
       <c r="D13" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -1002,16 +999,16 @@
       <c r="N13" s="2"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A14" s="11"/>
+      <c r="A14" s="12"/>
       <c r="B14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -1024,22 +1021,22 @@
       <c r="N14" s="2"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A15" s="11"/>
+      <c r="A15" s="12"/>
       <c r="B15" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -1050,22 +1047,22 @@
       <c r="N15" s="2"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A16" s="11"/>
+      <c r="A16" s="12"/>
       <c r="B16" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -1076,22 +1073,22 @@
       <c r="N16" s="2"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A17" s="11"/>
+      <c r="A17" s="12"/>
       <c r="B17" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -1102,19 +1099,19 @@
       <c r="N17" s="2"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A18" s="11"/>
+      <c r="A18" s="12"/>
       <c r="B18" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="4"/>
@@ -1126,22 +1123,22 @@
       <c r="N18" s="2"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A19" s="11"/>
+      <c r="A19" s="12"/>
       <c r="B19" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -1152,22 +1149,22 @@
       <c r="N19" s="2"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A20" s="11"/>
+      <c r="A20" s="12"/>
       <c r="B20" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -1178,22 +1175,22 @@
       <c r="N20" s="2"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A21" s="11"/>
+      <c r="A21" s="12"/>
       <c r="B21" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -1204,15 +1201,15 @@
       <c r="N21" s="2"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A22" s="11"/>
-      <c r="B22" s="7" t="s">
+      <c r="A22" s="12"/>
+      <c r="B22" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>59</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -1226,11 +1223,11 @@
       <c r="N22" s="2"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A23" s="12"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
       <c r="D23" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
